--- a/data/trans_orig/IQ19B_M_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_M_R-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,249 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41,77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12,0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17,42</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,74</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.203890761588243</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.97123599260212</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.2203462372402501</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>41.76644058446869</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.211557825940439</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>17.42140273322448</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>27.74008881858143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,6</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,64; 21,45</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,66</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 90,43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,44</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 24,0</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,98; 66,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.06439548393376533</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>10.63422904954545</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.06970421717069537</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="n">
+        <v>11.53844642353621</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.07357318102590812</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>12.97832178328131</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6002089539993178</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>21.44542953666145</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6594228714392043</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
+        <v>86.46634526924827</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.4407749537663391</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>66.64089046508704</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,97</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,77</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,49</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,17</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,05</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,07</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13,07</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 3,34</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11,23; 15,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,44; 14,62</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14,94; 35,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 4,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,61; 15,26</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,31; 11,75</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10,47; 14,09</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,34; 3,45</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11,91; 14,74</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11,23; 12,9</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 27,79</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.614415512985205</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12.96924387486058</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12.76894196674047</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>21.49127410603494</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.995595156110717</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>13.1673603721194</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>11.04862833427643</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>12.07193352841018</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2.803539246400675</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>13.07351820261372</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>11.96097852393587</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>17.4503706502372</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,7</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,44</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,8</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14,67</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14,88</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2.043064008051998</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>11.2280758726691</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>11.43678039206261</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>14.9391000421261</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2.261514332227148</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.60785432469331</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10.3137417223676</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>10.46593257035289</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2.3404718224335</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>11.90665221920425</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>11.22590898227242</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>13.84379634095591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,24; 10,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12,81; 16,1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,45; 18,39</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12,87; 18,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,42; 14,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>13,48; 18,53</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,32; 17,6</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12,18; 16,04</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>7,78; 11,08</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>13,57; 16,5</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>13,77; 16,52</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,81; 16,04</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.337200675866744</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>15.39190392394031</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>14.62314271770738</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>35.60616728814824</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>4.058438299835216</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>15.2635611752341</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>11.74533777149976</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>14.08831769782452</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3.445381947309803</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>14.73578866845452</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.89861145333384</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>27.79059052411982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +901,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,94</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,93</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16,15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11,74</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20,28</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15,94</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,48</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.791081726645895</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>14.09582661692171</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>14.95915742751269</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14.60768045531746</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>10.70081620441501</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>15.43946695871188</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>14.80458929069659</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>13.61032003367688</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.103410719874883</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>14.66678725031715</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>14.88026988311333</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>14.12555273896982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 16,03</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16,86; 24,31</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 18,92</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13,71; 17,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8,65; 11,68</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,33; 25,41</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,01; 17,45</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14,39; 20,2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10,22; 13,3</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18,13; 23,31</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14,69; 17,44</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,34; 17,3</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.241345713684482</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>12.81022500678739</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>13.45130176228104</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>12.87311859026383</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>8.424404489390431</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>13.48301774553669</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>13.3174865973078</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>12.17712568187268</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7.777661054498681</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>13.56653840732894</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>13.77496266849013</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>12.80763447764934</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.998962537918249</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16.10006072260345</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.39359195807258</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18.39900915398258</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>14.24762908058788</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>18.53163126131213</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>17.60089386277454</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>16.04141650237166</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>11.08419847187612</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>16.50119811454968</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>16.52478102914362</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>16.03982480521924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>13.23439450085548</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19.97836465341644</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>16.27293263226705</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>14.93842978659048</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>9.933205990819472</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>20.5984989097034</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>15.56457115709439</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>16.14881811791351</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>11.73819905168021</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>20.28453700155361</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>15.9419628482656</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>15.47893583232946</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11.32435130884482</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>16.86108526719467</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>14.4494012877241</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>13.71275397532469</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8.650953208639118</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>17.32947891302939</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>14.00888944401083</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>14.38595005121215</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>10.21944652406415</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>18.13289774289036</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>14.68665422981422</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>14.33652706985335</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>16.03043935906489</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>24.31126824193034</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>18.91998130718855</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>17.08565264365913</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>11.67872523985739</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>25.41207281560989</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>17.451325711763</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>20.19999970230688</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>13.30463645155876</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>23.31138016301163</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>17.43986023109317</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>17.29773168231134</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,25</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,62</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,53</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,57</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17,05</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14,87</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>15,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4,6; 6,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,14; 19,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14,16; 16,57</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14,5; 18,62</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 5,55</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,74; 20,22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,61; 15,99</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13,91; 17,37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4,59; 5,64</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15,72; 18,53</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 15,75</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 16,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>5.249973449901451</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>16.62213626510309</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>15.16089878880592</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>15.79725990456561</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>4.840115162562335</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>17.52537706017931</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>14.56846267517851</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>15.16493001610354</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.055947562968088</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>17.05268512691747</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>14.87322135569804</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>15.50885210886059</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4.596931627998886</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>15.1437234049553</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>14.16443763935187</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>14.50345925567899</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.190196599461815</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>15.73778305865504</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>13.60681025171699</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>13.9102562724371</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>4.58709640348285</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>15.72072337637544</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>14.14032320797529</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>14.44710219567274</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.158440498945747</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>19.2930269677885</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.57261392492364</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>18.62238795250728</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.551690363258229</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>20.21717679961819</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>15.98785553990637</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>17.36835498816781</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.635146756189565</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>18.52972242268625</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>15.74783918042266</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>16.88593347316362</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1307,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
